--- a/output/pdf_financials_xlsx/REX.xlsx
+++ b/output/pdf_financials_xlsx/REX.xlsx
@@ -4555,40 +4555,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.405514</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.428575</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.440698</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.302255</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.660481</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.698916</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.999356</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.511354</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.808422</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>6.808422</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>6.808422</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.058562</v>
       </c>
     </row>
     <row r="93">
@@ -7312,7 +7312,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -8742,7 +8746,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -9356,7 +9364,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -9656,7 +9668,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>4.405514</v>
       </c>

--- a/output/pdf_financials_xlsx/REX.xlsx
+++ b/output/pdf_financials_xlsx/REX.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000681</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.023508</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.131701</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.221845</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.028678</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.051055</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003888</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.016633</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.013865</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.044097</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.009495999999999999</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.7e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1580,40 +1580,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.358506</v>
+        <v>-4.359187</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>11.271227</v>
+        <v>11.247719</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>29.565625</v>
+        <v>29.697326</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.437019</v>
+        <v>-4.658864</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.378987</v>
+        <v>-3.407665</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.107434</v>
+        <v>-2.158489</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.319668</v>
+        <v>-2.323556</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.54412</v>
+        <v>-2.560753</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.324684</v>
+        <v>-2.338549</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.331123</v>
+        <v>-2.37522</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.873627</v>
+        <v>-1.883123</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.303238</v>
+        <v>-3.303255</v>
       </c>
     </row>
     <row r="28">
@@ -1666,40 +1666,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.358506</v>
+        <v>-4.359187</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>11.271227</v>
+        <v>11.247719</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>29.567904</v>
+        <v>29.699605</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.416942</v>
+        <v>-4.638787</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.359167</v>
+        <v>-3.387845</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.094796</v>
+        <v>-2.145851</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.310215</v>
+        <v>-2.314103</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.537029</v>
+        <v>-2.553662</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.319367</v>
+        <v>-2.333232</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.327136</v>
+        <v>-2.371233</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.870636</v>
+        <v>-1.880132</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.301555</v>
+        <v>-3.301572</v>
       </c>
     </row>
     <row r="30">
@@ -1893,40 +1893,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.385952</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.535704</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.523133</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.387496</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.990351</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.9992220000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.242385</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5.627706</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.302296</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.126141</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.027907</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.069051</v>
       </c>
     </row>
     <row r="35">
@@ -1979,40 +1979,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.385952</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.535704</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.523133</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.387496</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.990351</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.9992220000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.242385</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>5.627706</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>3.302296</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.126141</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.027907</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.069051</v>
       </c>
     </row>
     <row r="37">
@@ -2495,40 +2495,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.689717</v>
+        <v>0.303765</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8.898118</v>
+        <v>8.362413999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.54419</v>
+        <v>0.021057</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.540152</v>
+        <v>0.152656</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.0194</v>
+        <v>0.029049</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.153639</v>
+        <v>0.154417</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.27453</v>
+        <v>0.032145</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.673852</v>
+        <v>0.046146</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.340837</v>
+        <v>0.038541</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.156165</v>
+        <v>0.030024</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.034039</v>
+        <v>0.006132</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.124168</v>
+        <v>0.055117</v>
       </c>
     </row>
     <row r="49">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">

--- a/output/pdf_financials_xlsx/REX.xlsx
+++ b/output/pdf_financials_xlsx/REX.xlsx
@@ -1103,7 +1103,7 @@
         <v>-12.796427</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4.437019</v>
+        <v>-0.144748</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1271,13 +1271,15 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-2.743206</v>
+        <v>-1.912048</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>16.769198</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>16.769198</v>
+        <v>-5.497971</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E20" s="3" t="n">
         <v>-4.292271</v>
@@ -1314,13 +1316,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.831158</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.9497370000000001</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>3.820771</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1785,7 +1787,7 @@
         <v>43.28143578902864</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-100</v>
+        <v>-3.26228037337681</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5366,10 +5368,10 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.055848</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.036777</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6379,10 +6381,10 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.055848</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.036777</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -6422,10 +6424,10 @@
         <v>-6.045453</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-4.077362</v>
+        <v>-4.13321</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-5.004738</v>
+        <v>-5.041515</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-1.8266</v>
@@ -12980,7 +12982,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -13490,7 +13496,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -15762,7 +15772,11 @@
           <t>Purchase of equipment (Note 4)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -16290,7 +16304,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>0.296748</v>
       </c>
@@ -24634,7 +24652,11 @@
           <t>Deferred income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -26530,7 +26552,11 @@
           <t>Deferred income tax recovery (Note 15)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -26678,7 +26704,11 @@
           <t>Income from discontinued operations (Note 6)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -29030,7 +29060,11 @@
           <t>Deferred income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -31864,7 +31898,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E347" s="5" t="n">
         <v>-1.912048</v>
       </c>
@@ -31938,7 +31976,11 @@
           <t>Loss from discontinued operations (Note 7)</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E348" s="5" t="n">
         <v>-0.831158</v>
       </c>
